--- a/docs/reclamacoes.xlsx
+++ b/docs/reclamacoes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55BB843C-7697-477F-A9D4-FCFAC368A74B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B102448D-2870-4402-B981-09567CFBF950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reclamacoes" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="86">
   <si>
     <t>ID</t>
   </si>
@@ -266,6 +266,21 @@
   </si>
   <si>
     <t>pagamento referente ao dano no colchão e briquedos</t>
+  </si>
+  <si>
+    <t>veiculo fiscalização</t>
+  </si>
+  <si>
+    <t>Clean Car</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reparo </t>
+  </si>
+  <si>
+    <t>reparo</t>
+  </si>
+  <si>
+    <t>pagamento referente a batida de trânsito (TPF)</t>
   </si>
 </sst>
 </file>
@@ -306,10 +321,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -612,7 +628,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L21"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -1360,6 +1376,41 @@
         <v>80</v>
       </c>
     </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>46169</v>
+      </c>
+      <c r="C22" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" t="s">
+        <v>83</v>
+      </c>
+      <c r="G22" t="s">
+        <v>84</v>
+      </c>
+      <c r="H22" s="3">
+        <v>10074.39</v>
+      </c>
+      <c r="I22" s="3">
+        <v>10074.39</v>
+      </c>
+      <c r="J22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22" t="s">
+        <v>27</v>
+      </c>
+      <c r="L22" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L1" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L21">
